--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104647_W21.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104647_W21.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.7676</v>
+        <v>4.2654</v>
       </c>
       <c r="E2" t="n">
-        <v>5.341</v>
+        <v>4.5912</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.5734</v>
+        <v>-0.3258</v>
       </c>
       <c r="G2" t="n">
-        <v>1.0011</v>
+        <v>0.9899</v>
       </c>
       <c r="H2" t="n">
-        <v>2.078</v>
+        <v>2.0684</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.0769</v>
+        <v>-1.0786</v>
       </c>
       <c r="J2" t="n">
-        <v>2.8018</v>
+        <v>2.7656</v>
       </c>
       <c r="K2" t="n">
-        <v>3.3697</v>
+        <v>3.3472</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.5679</v>
+        <v>-0.5816</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.8007</v>
+        <v>-1.7758</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.2917</v>
+        <v>-1.2788</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.509</v>
+        <v>-0.497</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="R2" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9687</v>
+        <v>0.4819</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8075</v>
+        <v>0.1019</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1612</v>
+        <v>0.3801</v>
       </c>
       <c r="V2" t="n">
-        <v>2.571</v>
+        <v>2.5659</v>
       </c>
       <c r="W2" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X2" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9612</v>
+        <v>1.8976</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.2557</v>
+        <v>0.0355</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2169</v>
+        <v>1.8621</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.0351</v>
+        <v>-0.0381</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8312</v>
+        <v>0.8274</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.8663</v>
+        <v>-0.8653999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1616</v>
+        <v>0.1472</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9107</v>
+        <v>0.8996</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.749</v>
+        <v>-0.7524</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.1967</v>
+        <v>-0.1852</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0795</v>
+        <v>-0.0722</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1172</v>
+        <v>-0.113</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4785</v>
+        <v>0.409</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4174</v>
+        <v>-0.1116</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8958</v>
+        <v>0.5206</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6105</v>
+        <v>0.6162</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.6105</v>
+        <v>0.6162</v>
       </c>
     </row>
     <row r="4">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2702</v>
+        <v>1.3289</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0896</v>
+        <v>0.1131</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1806</v>
+        <v>1.2158</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6213</v>
+        <v>0.6225000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>1.5701</v>
+        <v>1.5574</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.9488</v>
+        <v>-0.9349</v>
       </c>
       <c r="J4" t="n">
-        <v>1.7211</v>
+        <v>1.6928</v>
       </c>
       <c r="K4" t="n">
-        <v>2.3582</v>
+        <v>2.3335</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.6371</v>
+        <v>-0.6407</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.0998</v>
+        <v>-1.0703</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.788</v>
+        <v>-0.7761</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3117</v>
+        <v>-0.2942</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R4" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1754</v>
+        <v>-0.1067</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1875</v>
+        <v>-0.1165</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0121</v>
+        <v>0.0097</v>
       </c>
       <c r="V4" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="W4" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2354</v>
+        <v>1.1804</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7106</v>
+        <v>0.5419</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5247000000000001</v>
+        <v>0.6385</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3365</v>
+        <v>0.3514</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.4446</v>
+        <v>-0.437</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7811</v>
+        <v>0.7883</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2505</v>
+        <v>0.2496</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1385</v>
+        <v>0.1379</v>
       </c>
       <c r="L5" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M5" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.1018</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5831</v>
+        <v>-0.5749</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6691</v>
+        <v>0.6766</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1503</v>
+        <v>0.0779</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2994</v>
+        <v>0.1345</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1491</v>
+        <v>-0.0567</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="6">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7256</v>
+        <v>1.1531</v>
       </c>
       <c r="E6" t="n">
-        <v>2.1052</v>
+        <v>2.7425</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.3796</v>
+        <v>-1.5894</v>
       </c>
       <c r="G6" t="n">
-        <v>1.1951</v>
+        <v>1.2006</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7793</v>
+        <v>0.7756999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4159</v>
+        <v>0.4249</v>
       </c>
       <c r="J6" t="n">
-        <v>2.0741</v>
+        <v>2.0552</v>
       </c>
       <c r="K6" t="n">
-        <v>1.0319</v>
+        <v>1.0202</v>
       </c>
       <c r="L6" t="n">
-        <v>1.0422</v>
+        <v>1.035</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8789</v>
+        <v>-0.8546</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2526</v>
+        <v>-0.2446</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6263</v>
+        <v>-0.61</v>
       </c>
       <c r="P6" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R6" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4845</v>
+        <v>-0.0765</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8347</v>
+        <v>-0.1745</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3502</v>
+        <v>0.098</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.7997</v>
+        <v>-1.792</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.8924</v>
+        <v>-2.8814</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. TOBEY</t>
+          <t>C. ALOCEN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5843</v>
+        <v>1.0256</v>
       </c>
       <c r="E7" t="n">
-        <v>2.0717</v>
+        <v>0.2904</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.4874</v>
+        <v>0.7352</v>
       </c>
       <c r="G7" t="n">
-        <v>1.4062</v>
+        <v>0.0233</v>
       </c>
       <c r="H7" t="n">
-        <v>2.0939</v>
+        <v>1.1032</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6877</v>
+        <v>-1.0799</v>
       </c>
       <c r="J7" t="n">
-        <v>3.2096</v>
+        <v>0.423</v>
       </c>
       <c r="K7" t="n">
-        <v>3.3697</v>
+        <v>1.1754</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.1601</v>
+        <v>-0.7524</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.8034</v>
+        <v>-0.3997</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.2758</v>
+        <v>-0.0722</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5276</v>
+        <v>-0.3275</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2268</v>
+        <v>0.9105</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.5878</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8147</v>
+        <v>0.9105</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5024</v>
+        <v>0.09180000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2571</v>
+        <v>-0.1326</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2453</v>
+        <v>0.2243</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.5463</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.7071</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2534</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. ALOCEN</t>
+          <t>M. TOBEY</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3198</v>
+        <v>0.6745</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1178</v>
+        <v>2.0905</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4375</v>
+        <v>-1.4159</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0261</v>
+        <v>1.3946</v>
       </c>
       <c r="H8" t="n">
-        <v>1.1083</v>
+        <v>2.0829</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.0822</v>
+        <v>-0.6882</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4387</v>
+        <v>3.1676</v>
       </c>
       <c r="K8" t="n">
-        <v>1.1878</v>
+        <v>3.3472</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.749</v>
+        <v>-0.1796</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4126</v>
+        <v>-1.7729</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0795</v>
+        <v>-1.2643</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3331</v>
+        <v>-0.5086000000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9073</v>
+        <v>0.2276</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.5934</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9073</v>
+        <v>1.8211</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6137</v>
+        <v>-0.403</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5565</v>
+        <v>-0.1862</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0572</v>
+        <v>-0.2168</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.5447</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.7025</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="9">
@@ -1111,40 +1111,40 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8808</v>
+        <v>-0.8771</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0546</v>
+        <v>0.0545</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9354</v>
+        <v>-0.9315</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2119</v>
+        <v>0.2124</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1946</v>
+        <v>0.1952</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0546</v>
+        <v>0.0545</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1165,19 +1165,19 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. VILA</t>
+          <t>A. ALBICY</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4684</v>
+        <v>-2.0868</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4167</v>
+        <v>-0.7282999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0517</v>
+        <v>-1.3585</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.0419</v>
+        <v>-0.0134</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2106</v>
+        <v>-1.3128</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.8312</v>
+        <v>1.2994</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.1415</v>
+        <v>1.5451</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3565</v>
+        <v>-0.0485</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.4981</v>
+        <v>1.5935</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.9003</v>
+        <v>-1.5585</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5672</v>
+        <v>-1.2643</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3331</v>
+        <v>-0.2942</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.9073</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.361</v>
+        <v>-1.5934</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4537</v>
+        <v>1.5934</v>
       </c>
       <c r="S10" t="n">
-        <v>1.4808</v>
+        <v>-0.5969</v>
       </c>
       <c r="T10" t="n">
-        <v>1.0858</v>
+        <v>-0.2929</v>
       </c>
       <c r="U10" t="n">
-        <v>0.395</v>
+        <v>-0.3039</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.4764</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.387</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. ALBICY</t>
+          <t>E. VILA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.8291</v>
+        <v>-2.5348</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.248</v>
+        <v>-2.3091</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.5811</v>
+        <v>-0.2257</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.0273</v>
+        <v>-2.0447</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.3175</v>
+        <v>-0.2124</v>
       </c>
       <c r="I11" t="n">
-        <v>1.2902</v>
+        <v>-1.8323</v>
       </c>
       <c r="J11" t="n">
-        <v>1.5602</v>
+        <v>-1.1568</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.0417</v>
+        <v>0.348</v>
       </c>
       <c r="L11" t="n">
-        <v>1.6019</v>
+        <v>-1.5048</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.5875</v>
+        <v>-0.8879</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.2758</v>
+        <v>-0.5604</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.3117</v>
+        <v>-0.3275</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.5878</v>
+        <v>-1.3658</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5878</v>
+        <v>0.4553</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.3235</v>
+        <v>0.4204</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8347</v>
+        <v>0.2135</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4888</v>
+        <v>0.2069</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.4783</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.3856</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.8995</v>
+        <v>-6.5418</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.7581</v>
+        <v>-5.426</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.1414</v>
+        <v>-1.1158</v>
       </c>
       <c r="G12" t="n">
-        <v>-5.176</v>
+        <v>-5.1851</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.8036</v>
+        <v>-2.8059</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.3724</v>
+        <v>-2.3792</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.6121</v>
+        <v>-3.6395</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.2205</v>
+        <v>-2.231</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.3915</v>
+        <v>-1.4084</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.5639</v>
+        <v>-1.5457</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.5831</v>
+        <v>-0.5749</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.9808</v>
+        <v>-0.9708</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R12" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2037</v>
+        <v>-0.8316</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9043</v>
+        <v>-0.5298</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2994</v>
+        <v>-0.3017</v>
       </c>
       <c r="V12" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W12" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.213699999999999</v>
+        <v>-0.5150000000000006</v>
       </c>
       <c r="E13" t="n">
-        <v>1.5764</v>
+        <v>1.996200000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.7903</v>
+        <v>-2.511</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.4821</v>
+        <v>-2.486600000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>3.7018</v>
+        <v>3.664099999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>-6.1837</v>
+        <v>-6.1507</v>
       </c>
       <c r="J13" t="n">
-        <v>7.518599999999999</v>
+        <v>7.3043</v>
       </c>
       <c r="K13" t="n">
-        <v>10.4781</v>
+        <v>10.3467</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.9593</v>
+        <v>-3.0425</v>
       </c>
       <c r="M13" t="n">
-        <v>-10.0005</v>
+        <v>-9.790900000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>-6.7763</v>
+        <v>-6.682699999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>-3.2241</v>
+        <v>-3.1083</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="Q13" t="n">
-        <v>-11.3416</v>
+        <v>-11.3815</v>
       </c>
       <c r="R13" t="n">
-        <v>13.61</v>
+        <v>13.658</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.2249</v>
+        <v>-0.5337000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.7995</v>
+        <v>-1.0942</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5745</v>
+        <v>0.5605</v>
       </c>
       <c r="V13" t="n">
-        <v>0.2249000000000005</v>
+        <v>0.2292000000000006</v>
       </c>
       <c r="W13" t="n">
-        <v>7.198899999999999</v>
+        <v>7.167800000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>-6.974099999999999</v>
+        <v>-6.9386</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.9732</v>
+        <v>7.3021</v>
       </c>
       <c r="E14" t="n">
-        <v>5.8778</v>
+        <v>6.5469</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0954</v>
+        <v>0.7552</v>
       </c>
       <c r="G14" t="n">
-        <v>4.2913</v>
+        <v>4.2916</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.9757</v>
+        <v>-0.9601</v>
       </c>
       <c r="I14" t="n">
-        <v>5.267</v>
+        <v>5.2517</v>
       </c>
       <c r="J14" t="n">
-        <v>4.847</v>
+        <v>4.8212</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1905</v>
+        <v>0.1896</v>
       </c>
       <c r="L14" t="n">
-        <v>4.6565</v>
+        <v>4.6316</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.5557</v>
+        <v>-0.5296</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.1662</v>
+        <v>-1.1497</v>
       </c>
       <c r="O14" t="n">
-        <v>0.6105</v>
+        <v>0.6201</v>
       </c>
       <c r="P14" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R14" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1839</v>
+        <v>0.1487</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.113</v>
+        <v>-0.4046</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9291</v>
+        <v>0.5532</v>
       </c>
       <c r="V14" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="W14" t="n">
-        <v>3.278</v>
+        <v>3.2684</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="15">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.5412</v>
+        <v>2.7685</v>
       </c>
       <c r="E15" t="n">
-        <v>3.9185</v>
+        <v>2.958</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3773</v>
+        <v>-0.1896</v>
       </c>
       <c r="G15" t="n">
-        <v>1.8045</v>
+        <v>1.8082</v>
       </c>
       <c r="H15" t="n">
-        <v>1.1168</v>
+        <v>1.1199</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6877</v>
+        <v>0.6882</v>
       </c>
       <c r="J15" t="n">
-        <v>2.0248</v>
+        <v>2.0062</v>
       </c>
       <c r="K15" t="n">
-        <v>1.7317</v>
+        <v>1.7237</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2931</v>
+        <v>0.2826</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.2203</v>
+        <v>-0.1981</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6149</v>
+        <v>-0.6037</v>
       </c>
       <c r="O15" t="n">
-        <v>0.3946</v>
+        <v>0.4057</v>
       </c>
       <c r="P15" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S15" t="n">
-        <v>1.4684</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>1.733</v>
+        <v>0.794</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2646</v>
+        <v>-0.11</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W15" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E. TAVARES</t>
+          <t>S. LLULL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.7153</v>
+        <v>1.3568</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0412</v>
+        <v>0.8703</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3259</v>
+        <v>0.4866</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.8597</v>
+        <v>-0.4493</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.4169</v>
+        <v>0.3853</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5572</v>
+        <v>-0.8345</v>
       </c>
       <c r="J16" t="n">
-        <v>0.136</v>
+        <v>-0.1354</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.1252</v>
+        <v>1.1614</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2612</v>
+        <v>-1.2967</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.9957</v>
+        <v>-0.3139</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.2917</v>
+        <v>-0.7761</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2959</v>
+        <v>0.4622</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5878</v>
+        <v>0.4553</v>
       </c>
       <c r="S16" t="n">
-        <v>1.7999</v>
+        <v>0.2614</v>
       </c>
       <c r="T16" t="n">
-        <v>2.1716</v>
+        <v>-0.0838</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3717</v>
+        <v>0.3452</v>
       </c>
       <c r="V16" t="n">
-        <v>0.3214</v>
+        <v>1.0895</v>
       </c>
       <c r="W16" t="n">
-        <v>0.8678</v>
+        <v>1.0895</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.5463</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1735,40 +1735,40 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.187</v>
+        <v>0.8133</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7059</v>
+        <v>1.2299</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.519</v>
+        <v>-0.4166</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3184</v>
+        <v>0.3207</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7128</v>
+        <v>0.7123</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3945</v>
+        <v>-0.3916</v>
       </c>
       <c r="J17" t="n">
-        <v>1.1283</v>
+        <v>1.1232</v>
       </c>
       <c r="K17" t="n">
-        <v>1.091</v>
+        <v>1.0859</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8099</v>
+        <v>-0.8025</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3781</v>
+        <v>-0.3736</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4318</v>
+        <v>-0.4289</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -1780,28 +1780,28 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.483</v>
+        <v>0.1057</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5777</v>
+        <v>0.1067</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.09470000000000001</v>
+        <v>-0.0011</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. LLULL</t>
+          <t>A. ABALDE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8703</v>
+        <v>0.5961</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4372</v>
+        <v>0.5846</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4331</v>
+        <v>0.0115</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4338</v>
+        <v>-0.3642</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3926</v>
+        <v>-0.0689</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.8264</v>
+        <v>-0.2953</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.0989</v>
+        <v>0.3538</v>
       </c>
       <c r="K18" t="n">
-        <v>1.1806</v>
+        <v>1.3822</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.2796</v>
+        <v>-1.0284</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.3348</v>
+        <v>-0.718</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.788</v>
+        <v>-1.4511</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4532</v>
+        <v>0.7331</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4537</v>
+        <v>1.1382</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4537</v>
+        <v>1.1382</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2423</v>
+        <v>-0.1778</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5565</v>
+        <v>-0.3139</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3142</v>
+        <v>0.1361</v>
       </c>
       <c r="V18" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0927</v>
+        <v>0.5447</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. ABALDE</t>
+          <t>E. TAVARES</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1034</v>
+        <v>0.3445</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0219</v>
+        <v>0.3619</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0815</v>
+        <v>-0.0174</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.3572</v>
+        <v>-0.8592</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0693</v>
+        <v>-1.4242</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2879</v>
+        <v>0.5649</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3799</v>
+        <v>0.1153</v>
       </c>
       <c r="K19" t="n">
-        <v>1.3956</v>
+        <v>-0.1454</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.0157</v>
+        <v>0.2607</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7371</v>
+        <v>-0.9745</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.4648</v>
+        <v>-1.2788</v>
       </c>
       <c r="O19" t="n">
-        <v>0.7277</v>
+        <v>0.3043</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1342</v>
+        <v>0.4553</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1342</v>
+        <v>1.5934</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6735</v>
+        <v>0.433</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9043</v>
+        <v>0.5245</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2308</v>
+        <v>-0.0915</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.3155</v>
       </c>
       <c r="W19" t="n">
-        <v>0.5463</v>
+        <v>0.8603</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="20">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4522</v>
+        <v>-0.0704</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2813</v>
+        <v>0.18</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1709</v>
+        <v>-0.2504</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4149</v>
+        <v>0.4208</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2728</v>
+        <v>-0.2674</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6877</v>
+        <v>0.6882</v>
       </c>
       <c r="J20" t="n">
-        <v>1.2007</v>
+        <v>1.1929</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1212</v>
+        <v>0.1207</v>
       </c>
       <c r="L20" t="n">
-        <v>1.0795</v>
+        <v>1.0722</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.7858000000000001</v>
+        <v>-0.772</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.394</v>
+        <v>-0.3881</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3918</v>
+        <v>-0.384</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1866</v>
+        <v>0.1917</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3478</v>
+        <v>0.1253</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1612</v>
+        <v>0.0664</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.4544</v>
+        <v>-1.2342</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.1699</v>
+        <v>-0.8421</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2845</v>
+        <v>-0.3921</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0629</v>
+        <v>0.0698</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.5901999999999999</v>
+        <v>-0.5888</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6531</v>
+        <v>0.6587</v>
       </c>
       <c r="J21" t="n">
-        <v>1.0109</v>
+        <v>1.001</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3392</v>
+        <v>0.3308</v>
       </c>
       <c r="L21" t="n">
-        <v>0.6717</v>
+        <v>0.6703</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.948</v>
+        <v>-0.9312</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.9294</v>
+        <v>-0.9196</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.0186</v>
+        <v>-0.0116</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.9488</v>
+        <v>-2.9592</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2075</v>
+        <v>0.021</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4174</v>
+        <v>-0.0629</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2099</v>
+        <v>0.0838</v>
       </c>
       <c r="V21" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="W21" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.9323</v>
+        <v>-1.7969</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.3778</v>
+        <v>-1.3825</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5545</v>
+        <v>-0.4144</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.1035</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.3594</v>
+        <v>-0.3536</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2559</v>
+        <v>0.2593</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.1381</v>
+        <v>-0.1287</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.394</v>
+        <v>-0.3881</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2559</v>
+        <v>0.2593</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2825</v>
+        <v>-0.1579</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2782</v>
+        <v>-0.2788</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0042</v>
+        <v>0.1209</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.0462</v>
+        <v>-2.2368</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.0472</v>
+        <v>-3.081</v>
       </c>
       <c r="F23" t="n">
-        <v>1.001</v>
+        <v>0.8442</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.6029</v>
+        <v>-1.6074</v>
       </c>
       <c r="H23" t="n">
-        <v>0.287</v>
+        <v>0.2954</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.89</v>
+        <v>-1.9028</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.5913</v>
+        <v>-0.6185</v>
       </c>
       <c r="K23" t="n">
-        <v>1.4373</v>
+        <v>1.4307</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.0286</v>
+        <v>-2.0491</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.0116</v>
+        <v>-0.989</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.1503</v>
+        <v>-1.1353</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1387</v>
+        <v>0.1463</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R23" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1712</v>
+        <v>-0.0163</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1875</v>
+        <v>-0.1862</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3587</v>
+        <v>0.1699</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.1952</v>
+        <v>-2.8925</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.5259</v>
+        <v>-2.3064</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.6693</v>
+        <v>-0.5861</v>
       </c>
       <c r="G24" t="n">
-        <v>0.8454</v>
+        <v>0.856</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0057</v>
+        <v>0.0112</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8397</v>
+        <v>0.8448</v>
       </c>
       <c r="J24" t="n">
-        <v>0.7007</v>
+        <v>0.6978</v>
       </c>
       <c r="K24" t="n">
-        <v>0.5888</v>
+        <v>0.5861</v>
       </c>
       <c r="L24" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M24" t="n">
-        <v>0.1446</v>
+        <v>0.1583</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.5831</v>
+        <v>-0.5749</v>
       </c>
       <c r="O24" t="n">
-        <v>0.7277</v>
+        <v>0.7331</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R24" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2032</v>
+        <v>0.0953</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3478</v>
+        <v>-0.1116</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1446</v>
+        <v>0.2069</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.2495</v>
+        <v>-2.2504</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.6105</v>
+        <v>-0.6162</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.0965</v>
+        <v>-3.7386</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.8105</v>
+        <v>-2.6085</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.2859</v>
+        <v>-1.1301</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.8982</v>
+        <v>-1.906</v>
       </c>
       <c r="H25" t="n">
-        <v>-2.5325</v>
+        <v>-2.525</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6343</v>
+        <v>0.619</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.7721</v>
+        <v>-0.8011</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.2091</v>
+        <v>-1.2173</v>
       </c>
       <c r="L25" t="n">
-        <v>0.437</v>
+        <v>0.4162</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.1261</v>
+        <v>-1.1048</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.3234</v>
+        <v>-1.3077</v>
       </c>
       <c r="O25" t="n">
-        <v>0.1973</v>
+        <v>0.2028</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R25" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.718</v>
+        <v>-0.3578</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.9043</v>
+        <v>-0.6692</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1863</v>
+        <v>0.3115</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>1.213600000000002</v>
+        <v>1.211899999999998</v>
       </c>
       <c r="E26" t="n">
-        <v>2.789899999999997</v>
+        <v>2.5111</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.5763</v>
+        <v>-1.2992</v>
       </c>
       <c r="G26" t="n">
-        <v>2.482099999999999</v>
+        <v>2.486800000000001</v>
       </c>
       <c r="H26" t="n">
-        <v>-3.7019</v>
+        <v>-3.6639</v>
       </c>
       <c r="I26" t="n">
-        <v>6.1838</v>
+        <v>6.150599999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>10.0006</v>
+        <v>9.790900000000002</v>
       </c>
       <c r="K26" t="n">
-        <v>6.776199999999999</v>
+        <v>6.682900000000001</v>
       </c>
       <c r="L26" t="n">
-        <v>3.2244</v>
+        <v>3.1083</v>
       </c>
       <c r="M26" t="n">
-        <v>-7.5185</v>
+        <v>-7.304</v>
       </c>
       <c r="N26" t="n">
-        <v>-10.4779</v>
+        <v>-10.3467</v>
       </c>
       <c r="O26" t="n">
-        <v>2.9593</v>
+        <v>3.0424</v>
       </c>
       <c r="P26" t="n">
-        <v>-2.268199999999999</v>
+        <v>-2.2762</v>
       </c>
       <c r="Q26" t="n">
-        <v>-13.6101</v>
+        <v>-13.6581</v>
       </c>
       <c r="R26" t="n">
-        <v>11.3418</v>
+        <v>11.3818</v>
       </c>
       <c r="S26" t="n">
-        <v>1.225</v>
+        <v>1.231</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.5744999999999996</v>
+        <v>-0.5605</v>
       </c>
       <c r="U26" t="n">
-        <v>1.7996</v>
+        <v>1.7913</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.2249999999999996</v>
+        <v>-0.2293000000000001</v>
       </c>
       <c r="W26" t="n">
-        <v>6.974</v>
+        <v>6.9387</v>
       </c>
       <c r="X26" t="n">
-        <v>-7.1989</v>
+        <v>-7.1678</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104647_W21.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104647_W21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104647_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0.6162</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104647_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104647_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104647_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-2.8814</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104647_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104647_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104647_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104647_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104647_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104647_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104647_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-6.9386</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104647_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104647_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104647_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104647_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104647_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104647_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104647_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104647_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104647_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104647_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104647_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104647_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-7.1678</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
